--- a/r5-ELGA-MOPED-339-Operation--erweitern-um-Hauptversichertenlogik/StructureDefinition-MOPEDEncounterSV.xlsx
+++ b/r5-ELGA-MOPED-339-Operation--erweitern-um-Hauptversichertenlogik/StructureDefinition-MOPEDEncounterSV.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-06T12:43:28+00:00</t>
+    <t>2025-02-07T07:29:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1182,49 +1182,49 @@
     <t>Encounter.class.text</t>
   </si>
   <si>
-    <t>Encounter.class:Aufnahmeart</t>
-  </si>
-  <si>
-    <t>Aufnahmeart</t>
-  </si>
-  <si>
-    <t>http://example.org/ValueSet/moped-aufnahmeart-valueset</t>
-  </si>
-  <si>
-    <t>Encounter.class:Aufnahmeart.id</t>
-  </si>
-  <si>
-    <t>Encounter.class:Aufnahmeart.extension</t>
-  </si>
-  <si>
-    <t>Encounter.class:Aufnahmeart.coding</t>
-  </si>
-  <si>
-    <t>Encounter.class:Aufnahmeart.coding.id</t>
-  </si>
-  <si>
-    <t>Encounter.class:Aufnahmeart.coding.extension</t>
-  </si>
-  <si>
-    <t>Encounter.class:Aufnahmeart.coding.system</t>
+    <t>Encounter.class:Aufnahmeart2</t>
+  </si>
+  <si>
+    <t>Aufnahmeart2</t>
+  </si>
+  <si>
+    <t>http://example.org/ValueSet/moped-aufnahmeart2-valueset</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart2.id</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart2.extension</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart2.coding</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart2.coding.id</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart2.coding.extension</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart2.coding.system</t>
   </si>
   <si>
     <t>http://tbd.at/moped-ext-aufnahmeart</t>
   </si>
   <si>
-    <t>Encounter.class:Aufnahmeart.coding.version</t>
-  </si>
-  <si>
-    <t>Encounter.class:Aufnahmeart.coding.code</t>
-  </si>
-  <si>
-    <t>Encounter.class:Aufnahmeart.coding.display</t>
-  </si>
-  <si>
-    <t>Encounter.class:Aufnahmeart.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Encounter.class:Aufnahmeart.text</t>
+    <t>Encounter.class:Aufnahmeart2.coding.version</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart2.coding.code</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart2.coding.display</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart2.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart2.text</t>
   </si>
   <si>
     <t>Encounter.priority</t>
@@ -2063,20 +2063,20 @@
     <t>Encounter.admission.extension</t>
   </si>
   <si>
-    <t>Encounter.admission.extension:zugangsart</t>
-  </si>
-  <si>
-    <t>zugangsart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-zugangsart}
+    <t>Encounter.admission.extension:aufnahmeart</t>
+  </si>
+  <si>
+    <t>aufnahmeart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-aufnahmeart}
 </t>
   </si>
   <si>
-    <t>Zugangsart</t>
-  </si>
-  <si>
-    <t>MOPED Extension für die Art des Zugangs.</t>
+    <t>Aufnahmeart</t>
+  </si>
+  <si>
+    <t>MOPED Extension für die Aufnahmeart.</t>
   </si>
   <si>
     <t>Encounter.admission.extension:transportart</t>
